--- a/resources/templates/standard/F2100-11.xlsx
+++ b/resources/templates/standard/F2100-11.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="69">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>자격 인증 교육 및 평가서</t>
   </si>
@@ -1026,12 +1029,14 @@
       <c r="BE1" s="1"/>
     </row>
     <row r="2" ht="17.15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
-      <c r="A2" s="2"/>
+      <c r="A2" s="2" t="s">
+        <v>0</v>
+      </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="3" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
@@ -1052,21 +1057,21 @@
       <c r="V2" s="3"/>
       <c r="W2" s="3"/>
       <c r="X2" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Z2" s="5"/>
       <c r="AA2" s="5"/>
       <c r="AB2" s="5" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AC2" s="5"/>
       <c r="AD2" s="5"/>
       <c r="AE2" s="1"/>
       <c r="AF2" s="6" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2" s="6"/>
       <c r="AH2" s="6"/>
@@ -1079,7 +1084,7 @@
       <c r="AM2" s="7"/>
       <c r="AN2" s="7"/>
       <c r="AO2" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP2" s="6"/>
       <c r="AQ2" s="6"/>
@@ -1142,7 +1147,7 @@
       <c r="AM3" s="7"/>
       <c r="AN3" s="7"/>
       <c r="AO3" s="6" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AP3" s="6"/>
       <c r="AQ3" s="6"/>
@@ -1205,7 +1210,7 @@
       <c r="AM4" s="7"/>
       <c r="AN4" s="7"/>
       <c r="AO4" s="6" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP4" s="6"/>
       <c r="AQ4" s="6"/>
@@ -1226,7 +1231,7 @@
     </row>
     <row r="5" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
@@ -1238,7 +1243,7 @@
       <c r="I5" s="10"/>
       <c r="J5" s="10"/>
       <c r="K5" s="11" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L5" s="11"/>
       <c r="M5" s="11"/>
@@ -1250,7 +1255,7 @@
       <c r="S5" s="10"/>
       <c r="T5" s="10"/>
       <c r="U5" s="11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
@@ -1291,7 +1296,7 @@
     </row>
     <row r="6" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -1303,7 +1308,7 @@
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
       <c r="K6" s="14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L6" s="14"/>
       <c r="M6" s="14"/>
@@ -1315,7 +1320,7 @@
       <c r="S6" s="13"/>
       <c r="T6" s="13"/>
       <c r="U6" s="14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="V6" s="14"/>
       <c r="W6" s="14"/>
@@ -1356,7 +1361,7 @@
     </row>
     <row r="7" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="12"/>
@@ -1378,7 +1383,7 @@
       <c r="S7" s="13"/>
       <c r="T7" s="13"/>
       <c r="U7" s="14" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V7" s="14"/>
       <c r="W7" s="14"/>
@@ -1422,7 +1427,7 @@
     </row>
     <row r="8" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A8" s="17" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B8" s="17"/>
       <c r="C8" s="17"/>
@@ -1542,7 +1547,7 @@
     </row>
     <row r="10" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="12"/>
       <c r="C10" s="12"/>
@@ -1603,7 +1608,7 @@
     </row>
     <row r="11" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -1624,14 +1629,14 @@
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
       <c r="T11" s="21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="U11" s="21"/>
       <c r="V11" s="21"/>
       <c r="W11" s="21"/>
       <c r="X11" s="21"/>
       <c r="Y11" s="21" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Z11" s="21"/>
       <c r="AA11" s="21"/>
@@ -1668,7 +1673,7 @@
     </row>
     <row r="12" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A12" s="22" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -1847,10 +1852,10 @@
     </row>
     <row r="15" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A15" s="22" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" s="25"/>
       <c r="D15" s="25"/>
@@ -1861,7 +1866,7 @@
       <c r="I15" s="25"/>
       <c r="J15" s="25"/>
       <c r="K15" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L15" s="25"/>
       <c r="M15" s="25"/>
@@ -1872,7 +1877,7 @@
       <c r="R15" s="25"/>
       <c r="S15" s="25"/>
       <c r="T15" s="25" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="U15" s="25"/>
       <c r="V15" s="25"/>
@@ -1883,7 +1888,7 @@
       <c r="AA15" s="25"/>
       <c r="AB15" s="25"/>
       <c r="AC15" s="25" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD15" s="25"/>
       <c r="AE15" s="1"/>
@@ -2388,7 +2393,7 @@
     </row>
     <row r="24" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B24" s="26"/>
       <c r="C24" s="26"/>
@@ -2449,7 +2454,7 @@
     </row>
     <row r="25" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A25" s="20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -2470,14 +2475,14 @@
       <c r="R25" s="20"/>
       <c r="S25" s="20"/>
       <c r="T25" s="21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="U25" s="21"/>
       <c r="V25" s="21"/>
       <c r="W25" s="21"/>
       <c r="X25" s="21"/>
       <c r="Y25" s="21" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="Z25" s="21"/>
       <c r="AA25" s="21"/>
@@ -2511,18 +2516,18 @@
       <c r="BC25" s="1"/>
       <c r="BD25" s="1"/>
       <c r="BE25" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A26" s="27" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C26" s="29" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D26" s="29"/>
       <c r="E26" s="29"/>
@@ -2541,7 +2546,7 @@
       <c r="R26" s="29"/>
       <c r="S26" s="29"/>
       <c r="T26" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U26" s="30"/>
       <c r="V26" s="30"/>
@@ -2585,7 +2590,7 @@
       <c r="A27" s="27"/>
       <c r="B27" s="28"/>
       <c r="C27" s="32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D27" s="32"/>
       <c r="E27" s="32"/>
@@ -2604,7 +2609,7 @@
       <c r="R27" s="32"/>
       <c r="S27" s="32"/>
       <c r="T27" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U27" s="33"/>
       <c r="V27" s="33"/>
@@ -2648,7 +2653,7 @@
       <c r="A28" s="27"/>
       <c r="B28" s="28"/>
       <c r="C28" s="32" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D28" s="32"/>
       <c r="E28" s="32"/>
@@ -2667,7 +2672,7 @@
       <c r="R28" s="32"/>
       <c r="S28" s="32"/>
       <c r="T28" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U28" s="33"/>
       <c r="V28" s="33"/>
@@ -2711,7 +2716,7 @@
       <c r="A29" s="27"/>
       <c r="B29" s="28"/>
       <c r="C29" s="32" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D29" s="32"/>
       <c r="E29" s="32"/>
@@ -2730,7 +2735,7 @@
       <c r="R29" s="32"/>
       <c r="S29" s="32"/>
       <c r="T29" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U29" s="33"/>
       <c r="V29" s="33"/>
@@ -2774,7 +2779,7 @@
       <c r="A30" s="27"/>
       <c r="B30" s="28"/>
       <c r="C30" s="34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30" s="34"/>
       <c r="E30" s="34"/>
@@ -2793,7 +2798,7 @@
       <c r="R30" s="34"/>
       <c r="S30" s="34"/>
       <c r="T30" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U30" s="35"/>
       <c r="V30" s="35"/>
@@ -2835,13 +2840,13 @@
     </row>
     <row r="31" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A31" s="27" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="28" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C31" s="29" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D31" s="29"/>
       <c r="E31" s="29"/>
@@ -2860,7 +2865,7 @@
       <c r="R31" s="29"/>
       <c r="S31" s="29"/>
       <c r="T31" s="30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="U31" s="30"/>
       <c r="V31" s="30"/>
@@ -2904,7 +2909,7 @@
       <c r="A32" s="27"/>
       <c r="B32" s="28"/>
       <c r="C32" s="32" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D32" s="32"/>
       <c r="E32" s="32"/>
@@ -2923,7 +2928,7 @@
       <c r="R32" s="32"/>
       <c r="S32" s="32"/>
       <c r="T32" s="33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="U32" s="33"/>
       <c r="V32" s="33"/>
@@ -2967,7 +2972,7 @@
       <c r="A33" s="27"/>
       <c r="B33" s="28"/>
       <c r="C33" s="32" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D33" s="32"/>
       <c r="E33" s="32"/>
@@ -2986,7 +2991,7 @@
       <c r="R33" s="32"/>
       <c r="S33" s="32"/>
       <c r="T33" s="33" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="U33" s="33"/>
       <c r="V33" s="33"/>
@@ -3030,7 +3035,7 @@
       <c r="A34" s="27"/>
       <c r="B34" s="28"/>
       <c r="C34" s="32" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D34" s="32"/>
       <c r="E34" s="32"/>
@@ -3049,7 +3054,7 @@
       <c r="R34" s="32"/>
       <c r="S34" s="32"/>
       <c r="T34" s="33" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="U34" s="33"/>
       <c r="V34" s="33"/>
@@ -3093,7 +3098,7 @@
       <c r="A35" s="27"/>
       <c r="B35" s="28"/>
       <c r="C35" s="34" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D35" s="34"/>
       <c r="E35" s="34"/>
@@ -3112,7 +3117,7 @@
       <c r="R35" s="34"/>
       <c r="S35" s="34"/>
       <c r="T35" s="35" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U35" s="35"/>
       <c r="V35" s="35"/>
@@ -3154,7 +3159,7 @@
     </row>
     <row r="36" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A36" s="36" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B36" s="36"/>
       <c r="C36" s="36"/>
@@ -3217,7 +3222,7 @@
     </row>
     <row r="37" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B37" s="20"/>
       <c r="C37" s="20"/>
@@ -3337,13 +3342,13 @@
     </row>
     <row r="39" ht="17.15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A39" s="22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B39" s="22"/>
       <c r="C39" s="22"/>
       <c r="D39" s="22"/>
       <c r="E39" s="38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F39" s="38"/>
       <c r="G39" s="38"/>
@@ -3518,13 +3523,13 @@
     </row>
     <row r="42" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
       <c r="D42" s="26"/>
       <c r="E42" s="39" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F42" s="39"/>
       <c r="G42" s="39"/>
@@ -3581,7 +3586,7 @@
     </row>
     <row r="43" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A43" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B43" s="20"/>
       <c r="C43" s="20"/>
@@ -3598,7 +3603,7 @@
       <c r="N43" s="40"/>
       <c r="O43" s="40"/>
       <c r="P43" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="Q43" s="21"/>
       <c r="R43" s="21"/>
@@ -3644,7 +3649,7 @@
     </row>
     <row r="44" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A44" s="41" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
@@ -3661,7 +3666,7 @@
       <c r="N44" s="42"/>
       <c r="O44" s="42"/>
       <c r="P44" s="43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Q44" s="43"/>
       <c r="R44" s="43"/>
@@ -3707,7 +3712,7 @@
     </row>
     <row r="45" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A45" s="45" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B45" s="45"/>
       <c r="C45" s="45"/>
@@ -3768,7 +3773,7 @@
     </row>
     <row r="46" ht="15" customHeight="1" spans="1:57" x14ac:dyDescent="0.25">
       <c r="A46" s="46" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B46" s="46"/>
       <c r="C46" s="46"/>
@@ -3780,19 +3785,19 @@
       <c r="I46" s="46"/>
       <c r="J46" s="46"/>
       <c r="K46" s="47" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="L46" s="47"/>
       <c r="M46" s="47"/>
       <c r="N46" s="47"/>
       <c r="O46" s="47" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="P46" s="47"/>
       <c r="Q46" s="47"/>
       <c r="R46" s="47"/>
       <c r="S46" s="47" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="T46" s="47"/>
       <c r="U46" s="47"/>
@@ -3802,7 +3807,7 @@
       <c r="Y46" s="47"/>
       <c r="Z46" s="47"/>
       <c r="AA46" s="47" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB46" s="47"/>
       <c r="AC46" s="47"/>
@@ -3847,7 +3852,7 @@
       <c r="I47" s="46"/>
       <c r="J47" s="46"/>
       <c r="K47" s="48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L47" s="48"/>
       <c r="M47" s="48"/>
@@ -3857,7 +3862,7 @@
       <c r="Q47" s="47"/>
       <c r="R47" s="47"/>
       <c r="S47" s="48" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="T47" s="48"/>
       <c r="U47" s="48"/>
@@ -3910,7 +3915,7 @@
       <c r="I48" s="46"/>
       <c r="J48" s="46"/>
       <c r="K48" s="49" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="L48" s="49"/>
       <c r="M48" s="49"/>
@@ -3920,7 +3925,7 @@
       <c r="Q48" s="47"/>
       <c r="R48" s="47"/>
       <c r="S48" s="49" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="T48" s="49"/>
       <c r="U48" s="49"/>
